--- a/rolling_rhb_pf.xlsx
+++ b/rolling_rhb_pf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dresi\Documents\Baseball Stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8E02A0-65A5-4627-BCC7-1E75B84FB40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF793728-D0C9-4988-B08A-87437121B384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{6B29E56E-3DBF-4A61-BE28-EE50A3A14621}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B29E56E-3DBF-4A61-BE28-EE50A3A14621}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -607,7 +607,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -655,7 +655,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -703,7 +703,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -751,7 +751,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -799,7 +799,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -847,7 +847,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -895,7 +895,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -943,7 +943,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -991,7 +991,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1039,7 +1039,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1087,7 +1087,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1135,7 +1135,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1183,7 +1183,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1231,7 +1231,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1279,7 +1279,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1327,7 +1327,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1375,7 +1375,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1423,7 +1423,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1471,7 +1471,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1519,7 +1519,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1567,7 +1567,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1615,7 +1615,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1663,7 +1663,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1711,7 +1711,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1759,7 +1759,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1807,7 +1807,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1855,7 +1855,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1903,7 +1903,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1951,7 +1951,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2366,37 +2366,37 @@
         <v>0</v>
       </c>
       <c r="D2" s="3">
+        <v>101</v>
+      </c>
+      <c r="E2" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="F2" s="6">
         <v>102</v>
       </c>
-      <c r="E2" s="5">
+      <c r="G2" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="H2" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="I2" s="7">
         <v>99</v>
       </c>
-      <c r="F2" s="6">
-        <v>104</v>
-      </c>
-      <c r="G2" s="4">
-        <v>101</v>
-      </c>
-      <c r="H2" s="5">
-        <v>99</v>
-      </c>
-      <c r="I2" s="7">
+      <c r="J2" s="8">
         <v>98</v>
       </c>
-      <c r="J2" s="8">
-        <v>96</v>
-      </c>
       <c r="K2" s="9">
-        <v>89</v>
+        <v>94.5</v>
       </c>
       <c r="L2" s="10">
-        <v>109</v>
+        <v>104.5</v>
       </c>
       <c r="M2" s="11">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="N2" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -2413,7 +2413,7 @@
         <v>100</v>
       </c>
       <c r="E3" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="F3" s="13">
         <v>100</v>
@@ -2428,19 +2428,19 @@
         <v>100</v>
       </c>
       <c r="J3" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K3" s="15">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="L3" s="16">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="M3" s="13">
         <v>100</v>
       </c>
       <c r="N3" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -2454,34 +2454,34 @@
         <v>0</v>
       </c>
       <c r="D4" s="14">
+        <v>98.5</v>
+      </c>
+      <c r="E4" s="8">
+        <v>98</v>
+      </c>
+      <c r="F4" s="17">
         <v>97</v>
       </c>
-      <c r="E4" s="8">
-        <v>96</v>
-      </c>
-      <c r="F4" s="17">
-        <v>94</v>
-      </c>
       <c r="G4" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="H4" s="7">
         <v>99</v>
       </c>
-      <c r="H4" s="7">
-        <v>98</v>
-      </c>
       <c r="I4" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J4" s="18">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="K4" s="17">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L4" s="9">
-        <v>81</v>
+        <v>90.5</v>
       </c>
       <c r="M4" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N4" s="13">
         <v>100</v>
@@ -2498,37 +2498,37 @@
         <v>0</v>
       </c>
       <c r="D5" s="3">
+        <v>101</v>
+      </c>
+      <c r="E5" s="12">
+        <v>101.5</v>
+      </c>
+      <c r="F5" s="6">
         <v>102</v>
       </c>
-      <c r="E5" s="12">
-        <v>103</v>
-      </c>
-      <c r="F5" s="6">
-        <v>104</v>
-      </c>
       <c r="G5" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="H5" s="3">
         <v>101</v>
       </c>
-      <c r="H5" s="3">
-        <v>102</v>
-      </c>
       <c r="I5" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="J5" s="19">
-        <v>107</v>
+        <v>103.5</v>
       </c>
       <c r="K5" s="20">
-        <v>49</v>
+        <v>74.5</v>
       </c>
       <c r="L5" s="19">
-        <v>107</v>
+        <v>103.5</v>
       </c>
       <c r="M5" s="17">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N5" s="21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -2542,37 +2542,37 @@
         <v>0</v>
       </c>
       <c r="D6" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="E6" s="11">
+        <v>103</v>
+      </c>
+      <c r="F6" s="3">
         <v>101</v>
       </c>
-      <c r="E6" s="11">
-        <v>106</v>
-      </c>
-      <c r="F6" s="3">
-        <v>102</v>
-      </c>
       <c r="G6" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="H6" s="3">
         <v>101</v>
       </c>
-      <c r="H6" s="3">
-        <v>102</v>
-      </c>
       <c r="I6" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J6" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K6" s="9">
-        <v>81</v>
+        <v>90.5</v>
       </c>
       <c r="L6" s="16">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="M6" s="12">
+        <v>101.5</v>
+      </c>
+      <c r="N6" s="11">
         <v>103</v>
-      </c>
-      <c r="N6" s="11">
-        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -2586,37 +2586,37 @@
         <v>0</v>
       </c>
       <c r="D7" s="14">
+        <v>98.5</v>
+      </c>
+      <c r="E7" s="14">
+        <v>98.5</v>
+      </c>
+      <c r="F7" s="17">
         <v>97</v>
       </c>
-      <c r="E7" s="14">
+      <c r="G7" s="8">
+        <v>98</v>
+      </c>
+      <c r="H7" s="17">
         <v>97</v>
       </c>
-      <c r="F7" s="17">
-        <v>94</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="I7" s="22">
         <v>96</v>
       </c>
-      <c r="H7" s="17">
-        <v>94</v>
-      </c>
-      <c r="I7" s="22">
-        <v>92</v>
-      </c>
       <c r="J7" s="9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K7" s="23">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="L7" s="24">
-        <v>111</v>
+        <v>105.5</v>
       </c>
       <c r="M7" s="6">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N7" s="24">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -2630,37 +2630,37 @@
         <v>0</v>
       </c>
       <c r="D8" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="E8" s="3">
         <v>101</v>
       </c>
-      <c r="E8" s="3">
-        <v>102</v>
-      </c>
       <c r="F8" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G8" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H8" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="I8" s="16">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="J8" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="K8" s="21">
+        <v>97.5</v>
+      </c>
+      <c r="L8" s="25">
+        <v>96.5</v>
+      </c>
+      <c r="M8" s="3">
+        <v>101</v>
+      </c>
+      <c r="N8" s="9">
         <v>95</v>
-      </c>
-      <c r="L8" s="25">
-        <v>93</v>
-      </c>
-      <c r="M8" s="3">
-        <v>102</v>
-      </c>
-      <c r="N8" s="9">
-        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -2674,37 +2674,37 @@
         <v>0</v>
       </c>
       <c r="D9" s="8">
+        <v>98</v>
+      </c>
+      <c r="E9" s="8">
+        <v>98</v>
+      </c>
+      <c r="F9" s="22">
         <v>96</v>
       </c>
-      <c r="E9" s="8">
-        <v>96</v>
-      </c>
-      <c r="F9" s="22">
-        <v>92</v>
-      </c>
       <c r="G9" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="H9" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I9" s="13">
         <v>100</v>
       </c>
       <c r="J9" s="9">
-        <v>81</v>
+        <v>90.5</v>
       </c>
       <c r="K9" s="24">
-        <v>131</v>
+        <v>115.5</v>
       </c>
       <c r="L9" s="17">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M9" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N9" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -2718,37 +2718,37 @@
         <v>0</v>
       </c>
       <c r="D10" s="12">
+        <v>101.5</v>
+      </c>
+      <c r="E10" s="6">
+        <v>102</v>
+      </c>
+      <c r="F10" s="11">
         <v>103</v>
       </c>
-      <c r="E10" s="6">
-        <v>104</v>
-      </c>
-      <c r="F10" s="11">
-        <v>106</v>
-      </c>
       <c r="G10" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="H10" s="19">
-        <v>107</v>
+        <v>103.5</v>
       </c>
       <c r="I10" s="16">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="J10" s="24">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="K10" s="24">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="L10" s="17">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M10" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="N10" s="21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -2762,37 +2762,37 @@
         <v>0</v>
       </c>
       <c r="D11" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="E11" s="14">
+        <v>98.5</v>
+      </c>
+      <c r="F11" s="3">
         <v>101</v>
       </c>
-      <c r="E11" s="14">
-        <v>97</v>
-      </c>
-      <c r="F11" s="3">
-        <v>102</v>
-      </c>
       <c r="G11" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H11" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I11" s="22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J11" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="K11" s="26">
-        <v>71</v>
+        <v>85.5</v>
       </c>
       <c r="L11" s="24">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="M11" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N11" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -2806,37 +2806,37 @@
         <v>0</v>
       </c>
       <c r="D12" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="E12" s="13">
         <v>100</v>
       </c>
       <c r="F12" s="17">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G12" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H12" s="13">
         <v>100</v>
       </c>
       <c r="I12" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="J12" s="16">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="K12" s="24">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="L12" s="27">
-        <v>79</v>
+        <v>89.5</v>
       </c>
       <c r="M12" s="9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N12" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -2850,37 +2850,37 @@
         <v>0</v>
       </c>
       <c r="D13" s="21">
+        <v>97.5</v>
+      </c>
+      <c r="E13" s="8">
+        <v>98</v>
+      </c>
+      <c r="F13" s="9">
         <v>95</v>
       </c>
-      <c r="E13" s="8">
-        <v>96</v>
-      </c>
-      <c r="F13" s="9">
-        <v>90</v>
-      </c>
       <c r="G13" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="H13" s="21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I13" s="21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J13" s="10">
-        <v>109</v>
+        <v>104.5</v>
       </c>
       <c r="K13" s="6">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L13" s="28">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="M13" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="N13" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2894,37 +2894,37 @@
         <v>0</v>
       </c>
       <c r="D14" s="22">
+        <v>96</v>
+      </c>
+      <c r="E14" s="21">
+        <v>97.5</v>
+      </c>
+      <c r="F14" s="9">
+        <v>92.5</v>
+      </c>
+      <c r="G14" s="25">
+        <v>96.5</v>
+      </c>
+      <c r="H14" s="9">
+        <v>95</v>
+      </c>
+      <c r="I14" s="9">
+        <v>95</v>
+      </c>
+      <c r="J14" s="9">
         <v>92</v>
       </c>
-      <c r="E14" s="21">
-        <v>95</v>
-      </c>
-      <c r="F14" s="9">
-        <v>85</v>
-      </c>
-      <c r="G14" s="25">
-        <v>93</v>
-      </c>
-      <c r="H14" s="9">
-        <v>90</v>
-      </c>
-      <c r="I14" s="9">
-        <v>90</v>
-      </c>
-      <c r="J14" s="9">
+      <c r="K14" s="15">
         <v>84</v>
       </c>
-      <c r="K14" s="15">
-        <v>68</v>
-      </c>
       <c r="L14" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="M14" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="N14" s="24">
-        <v>115</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -2941,7 +2941,7 @@
         <v>100</v>
       </c>
       <c r="E15" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="F15" s="13">
         <v>100</v>
@@ -2950,22 +2950,22 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I15" s="12">
+        <v>101.5</v>
+      </c>
+      <c r="J15" s="18">
+        <v>104</v>
+      </c>
+      <c r="K15" s="11">
         <v>103</v>
       </c>
-      <c r="J15" s="18">
-        <v>108</v>
-      </c>
-      <c r="K15" s="11">
-        <v>106</v>
-      </c>
       <c r="L15" s="9">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M15" s="17">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N15" s="13">
         <v>100</v>
@@ -2982,37 +2982,37 @@
         <v>0</v>
       </c>
       <c r="D16" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E16" s="13">
         <v>100</v>
       </c>
       <c r="F16" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G16" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="H16" s="25">
+        <v>96.5</v>
+      </c>
+      <c r="I16" s="25">
+        <v>96.5</v>
+      </c>
+      <c r="J16" s="9">
         <v>93</v>
       </c>
-      <c r="I16" s="25">
-        <v>93</v>
-      </c>
-      <c r="J16" s="9">
-        <v>86</v>
-      </c>
       <c r="K16" s="9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L16" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="M16" s="24">
-        <v>111</v>
+        <v>105.5</v>
       </c>
       <c r="N16" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -3026,37 +3026,37 @@
         <v>0</v>
       </c>
       <c r="D17" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="E17" s="7">
         <v>99</v>
       </c>
-      <c r="E17" s="7">
-        <v>98</v>
-      </c>
       <c r="F17" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="H17" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="I17" s="13">
         <v>100</v>
       </c>
       <c r="J17" s="17">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K17" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="L17" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="M17" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="N17" s="21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -3070,37 +3070,37 @@
         <v>0</v>
       </c>
       <c r="D18" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="E18" s="6">
+        <v>102</v>
+      </c>
+      <c r="F18" s="7">
         <v>99</v>
       </c>
-      <c r="E18" s="6">
-        <v>104</v>
-      </c>
-      <c r="F18" s="7">
-        <v>98</v>
-      </c>
       <c r="G18" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="H18" s="6">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I18" s="24">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="J18" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="K18" s="24">
-        <v>155</v>
+        <v>127.5</v>
       </c>
       <c r="L18" s="27">
-        <v>79</v>
+        <v>89.5</v>
       </c>
       <c r="M18" s="17">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N18" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -3114,37 +3114,37 @@
         <v>0</v>
       </c>
       <c r="D19" s="14">
+        <v>98.5</v>
+      </c>
+      <c r="E19" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="F19" s="17">
         <v>97</v>
       </c>
-      <c r="E19" s="5">
+      <c r="G19" s="8">
+        <v>98</v>
+      </c>
+      <c r="H19" s="8">
+        <v>98</v>
+      </c>
+      <c r="I19" s="14">
+        <v>98.5</v>
+      </c>
+      <c r="J19" s="9">
+        <v>92.5</v>
+      </c>
+      <c r="K19" s="29">
+        <v>86.5</v>
+      </c>
+      <c r="L19" s="24">
+        <v>105.5</v>
+      </c>
+      <c r="M19" s="7">
         <v>99</v>
       </c>
-      <c r="F19" s="17">
-        <v>94</v>
-      </c>
-      <c r="G19" s="8">
-        <v>96</v>
-      </c>
-      <c r="H19" s="8">
-        <v>96</v>
-      </c>
-      <c r="I19" s="14">
-        <v>97</v>
-      </c>
-      <c r="J19" s="9">
-        <v>85</v>
-      </c>
-      <c r="K19" s="29">
-        <v>73</v>
-      </c>
-      <c r="L19" s="24">
-        <v>111</v>
-      </c>
-      <c r="M19" s="7">
-        <v>98</v>
-      </c>
       <c r="N19" s="6">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -3161,34 +3161,34 @@
         <v>100</v>
       </c>
       <c r="E20" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F20" s="13">
         <v>100</v>
       </c>
       <c r="G20" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H20" s="13">
         <v>100</v>
       </c>
       <c r="I20" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J20" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K20" s="9">
-        <v>89</v>
+        <v>94.5</v>
       </c>
       <c r="L20" s="11">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M20" s="22">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N20" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -3202,37 +3202,37 @@
         <v>0</v>
       </c>
       <c r="D21" s="7">
+        <v>99</v>
+      </c>
+      <c r="E21" s="12">
+        <v>101.5</v>
+      </c>
+      <c r="F21" s="8">
         <v>98</v>
       </c>
-      <c r="E21" s="12">
-        <v>103</v>
-      </c>
-      <c r="F21" s="8">
-        <v>96</v>
-      </c>
       <c r="G21" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="H21" s="13">
         <v>100</v>
       </c>
       <c r="I21" s="16">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="J21" s="19">
-        <v>107</v>
+        <v>103.5</v>
       </c>
       <c r="K21" s="21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L21" s="26">
-        <v>71</v>
+        <v>85.5</v>
       </c>
       <c r="M21" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="N21" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -3246,37 +3246,37 @@
         <v>0</v>
       </c>
       <c r="D22" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="E22" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="F22" s="3">
         <v>101</v>
-      </c>
-      <c r="E22" s="4">
-        <v>101</v>
-      </c>
-      <c r="F22" s="3">
-        <v>102</v>
       </c>
       <c r="G22" s="13">
         <v>100</v>
       </c>
       <c r="H22" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="I22" s="8">
+        <v>98</v>
+      </c>
+      <c r="J22" s="22">
         <v>96</v>
       </c>
-      <c r="J22" s="22">
-        <v>92</v>
-      </c>
       <c r="K22" s="24">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="L22" s="24">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="M22" s="6">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N22" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -3290,37 +3290,37 @@
         <v>0</v>
       </c>
       <c r="D23" s="7">
+        <v>99</v>
+      </c>
+      <c r="E23" s="8">
         <v>98</v>
       </c>
-      <c r="E23" s="8">
-        <v>96</v>
-      </c>
       <c r="F23" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G23" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="H23" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="I23" s="21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J23" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K23" s="24">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="L23" s="6">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M23" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N23" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -3334,37 +3334,37 @@
         <v>0</v>
       </c>
       <c r="D24" s="6">
+        <v>102</v>
+      </c>
+      <c r="E24" s="3">
+        <v>101</v>
+      </c>
+      <c r="F24" s="18">
         <v>104</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="6">
         <v>102</v>
       </c>
-      <c r="F24" s="18">
-        <v>108</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="H24" s="11">
+        <v>103</v>
+      </c>
+      <c r="I24" s="19">
+        <v>103.5</v>
+      </c>
+      <c r="J24" s="18">
         <v>104</v>
       </c>
-      <c r="H24" s="11">
-        <v>106</v>
-      </c>
-      <c r="I24" s="19">
+      <c r="K24" s="24">
         <v>107</v>
-      </c>
-      <c r="J24" s="18">
-        <v>108</v>
-      </c>
-      <c r="K24" s="24">
-        <v>114</v>
       </c>
       <c r="L24" s="13">
         <v>100</v>
       </c>
       <c r="M24" s="17">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N24" s="6">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -3378,37 +3378,37 @@
         <v>0</v>
       </c>
       <c r="D25" s="6">
+        <v>102</v>
+      </c>
+      <c r="E25" s="7">
+        <v>99</v>
+      </c>
+      <c r="F25" s="18">
         <v>104</v>
       </c>
-      <c r="E25" s="7">
-        <v>98</v>
-      </c>
-      <c r="F25" s="18">
-        <v>108</v>
-      </c>
       <c r="G25" s="6">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H25" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I25" s="13">
         <v>100</v>
       </c>
       <c r="J25" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="K25" s="30">
-        <v>47</v>
+        <v>73.5</v>
       </c>
       <c r="L25" s="24">
-        <v>119</v>
+        <v>109.5</v>
       </c>
       <c r="M25" s="19">
-        <v>107</v>
+        <v>103.5</v>
       </c>
       <c r="N25" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -3422,37 +3422,37 @@
         <v>0</v>
       </c>
       <c r="D26" s="24">
-        <v>113</v>
+        <v>106.5</v>
       </c>
       <c r="E26" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="F26" s="24">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="G26" s="24">
+        <v>105</v>
+      </c>
+      <c r="H26" s="24">
+        <v>108</v>
+      </c>
+      <c r="I26" s="24">
+        <v>107</v>
+      </c>
+      <c r="J26" s="24">
         <v>110</v>
       </c>
-      <c r="H26" s="24">
-        <v>116</v>
-      </c>
-      <c r="I26" s="24">
-        <v>114</v>
-      </c>
-      <c r="J26" s="24">
-        <v>120</v>
-      </c>
       <c r="K26" s="24">
-        <v>221</v>
+        <v>160.5</v>
       </c>
       <c r="L26" s="24">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="M26" s="21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N26" s="9">
-        <v>87</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -3466,37 +3466,37 @@
         <v>0</v>
       </c>
       <c r="D27" s="6">
+        <v>102</v>
+      </c>
+      <c r="E27" s="16">
+        <v>102.5</v>
+      </c>
+      <c r="F27" s="18">
         <v>104</v>
       </c>
-      <c r="E27" s="16">
-        <v>105</v>
-      </c>
-      <c r="F27" s="18">
-        <v>108</v>
-      </c>
       <c r="G27" s="16">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="H27" s="18">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I27" s="10">
-        <v>109</v>
+        <v>104.5</v>
       </c>
       <c r="J27" s="24">
-        <v>113</v>
+        <v>106.5</v>
       </c>
       <c r="K27" s="24">
-        <v>181</v>
+        <v>140.5</v>
       </c>
       <c r="L27" s="31">
-        <v>91</v>
+        <v>95.5</v>
       </c>
       <c r="M27" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="N27" s="9">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -3510,37 +3510,37 @@
         <v>0</v>
       </c>
       <c r="D28" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28" s="13">
         <v>100</v>
       </c>
       <c r="F28" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G28" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="H28" s="7">
         <v>99</v>
       </c>
-      <c r="H28" s="7">
-        <v>98</v>
-      </c>
       <c r="I28" s="4">
+        <v>100.5</v>
+      </c>
+      <c r="J28" s="21">
+        <v>97.5</v>
+      </c>
+      <c r="K28" s="3">
         <v>101</v>
       </c>
-      <c r="J28" s="21">
-        <v>95</v>
-      </c>
-      <c r="K28" s="3">
-        <v>102</v>
-      </c>
       <c r="L28" s="9">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M28" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="N28" s="21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -3554,37 +3554,37 @@
         <v>0</v>
       </c>
       <c r="D29" s="3">
+        <v>101</v>
+      </c>
+      <c r="E29" s="5">
+        <v>99.5</v>
+      </c>
+      <c r="F29" s="6">
         <v>102</v>
       </c>
-      <c r="E29" s="5">
-        <v>99</v>
-      </c>
-      <c r="F29" s="6">
-        <v>104</v>
-      </c>
       <c r="G29" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="H29" s="4">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="I29" s="14">
-        <v>97</v>
+        <v>98.5</v>
       </c>
       <c r="J29" s="24">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="K29" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L29" s="16">
-        <v>105</v>
+        <v>102.5</v>
       </c>
       <c r="M29" s="6">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N29" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -3601,7 +3601,7 @@
         <v>100</v>
       </c>
       <c r="E30" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="F30" s="13">
         <v>100</v>
@@ -3613,16 +3613,16 @@
         <v>100</v>
       </c>
       <c r="I30" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J30" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K30" s="32">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L30" s="5">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="M30" s="13">
         <v>100</v>
@@ -3645,7 +3645,7 @@
         <v>100</v>
       </c>
       <c r="E31" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="F31" s="13">
         <v>100</v>
@@ -3654,25 +3654,25 @@
         <v>100</v>
       </c>
       <c r="H31" s="8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I31" s="25">
-        <v>93</v>
+        <v>96.5</v>
       </c>
       <c r="J31" s="31">
-        <v>91</v>
+        <v>95.5</v>
       </c>
       <c r="K31" s="33">
-        <v>57</v>
+        <v>78.5</v>
       </c>
       <c r="L31" s="24">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M31" s="24">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="N31" s="12">
-        <v>103</v>
+        <v>101.5</v>
       </c>
     </row>
   </sheetData>
